--- a/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Raccolta differenziata dei rifiuti.xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Raccolta differenziata dei rifiuti.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="125">
   <si>
     <r>
       <t xml:space="preserve">
@@ -157,7 +157,7 @@
     <t>Inserire una descrizione del servizio e delle tipologie di pagamenti che si potranno effettuare per il servizio.</t>
   </si>
   <si>
-    <t xml:space="preserve">Il servizio riguarda la raccolta differenziata dei rifiuti. 
+    <t xml:space="preserve">Il servizio riguarda la raccolta differenziata dei rifiuti.
 Tramite IO potrai:
 - ricevere comunicazioni e aggiornamento sul ritiro dei rifiuti;
 - ricevere eventuali avvisi di pagamento e pagarli in app;
@@ -709,7 +709,7 @@
         <rFont val="Titillium Web"/>
       </rPr>
       <t xml:space="preserve">
- Per ulteriori informazioni, [visita questo sito](URL).</t>
+Per ulteriori informazioni, [visita questo sito](URL).</t>
     </r>
   </si>
   <si>
@@ -1474,7 +1474,7 @@
       <rPr>
         <b/>
       </rPr>
-      <t>Allegato (Premium)</t>
+      <t>Allegato</t>
     </r>
     <r>
       <rPr/>
@@ -1571,19 +1571,8 @@
     </r>
   </si>
   <si>
-    <t>✨Messaggio Premium — Se hai un contratto Premium, ti consigliamo di configurare questo messaggio con promemoria Premium: i destinatari verranno avvisati dell‘avvicinarsi della scadenza tramite notifica push.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Promemoria automatici — Messaggi Premium
-Impostando il messaggio di Avviso di pagamento come Messaggio Premium, disponibile a seconda della tipologia di contratto sottoscritto dall’ente, non è necessario inviare il seguente messaggio di promemoria.
-Gli utenti che hanno dato il loro consenso, infatti, riceveranno automaticamente una notifica push sui loro dispositivi all’avvicinarsi della scadenza.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mancato pagamento
 Il seguente messaggio serve a sollecitare il cittadino per il mancato pagamento ma non costituisce in alcun modo un avviso a valore legale (i.e. notifica).</t>
-  </si>
-  <si>
-    <t>✨Messaggio Premium — Se hai un contratto Premium, ti consigliamo di configurare questo messaggio con promemoria Premium: i destinatari verranno avvisati dell‘avvicinarsi dell'appuntamento tramite notifica push.</t>
   </si>
 </sst>
 </file>
@@ -2558,16 +2547,16 @@
         <v>61</v>
       </c>
       <c r="I11" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="J11" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="K11" s="34" t="s">
         <v>124</v>
       </c>
-      <c r="J11" s="34" t="s">
-        <v>125</v>
-      </c>
-      <c r="K11" s="34" t="s">
-        <v>126</v>
-      </c>
       <c r="L11" s="34" t="s">
-        <v>127</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
